--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_valparaiso.xlsx
@@ -404,7 +404,7 @@
         <v>24.01511121142261</v>
       </c>
       <c r="D2">
-        <v>1.58371914893617</v>
+        <v>2.555753938278557</v>
       </c>
       <c r="E2">
         <v>23.9835697839499</v>
@@ -429,7 +429,7 @@
         <v>25.66312681556265</v>
       </c>
       <c r="D3">
-        <v>1.659213021491782</v>
+        <v>2.889638089995872</v>
       </c>
       <c r="E3">
         <v>21.59263110979052</v>
@@ -454,7 +454,7 @@
         <v>23.3457249070632</v>
       </c>
       <c r="D4">
-        <v>1.702863264511103</v>
+        <v>2.826543808600065</v>
       </c>
       <c r="E4">
         <v>22.28948221813858</v>
@@ -479,7 +479,7 @@
         <v>31.23844731977819</v>
       </c>
       <c r="D5">
-        <v>1.515406162464986</v>
+        <v>2.877659574468085</v>
       </c>
       <c r="E5">
         <v>20.93541202672606</v>
@@ -504,7 +504,7 @@
         <v>27.90387182910548</v>
       </c>
       <c r="D6">
-        <v>1.422409115572436</v>
+        <v>2.358524516419253</v>
       </c>
       <c r="E6">
         <v>24.89640497256132</v>
@@ -529,7 +529,7 @@
         <v>29.63610289504347</v>
       </c>
       <c r="D7">
-        <v>1.439427170687653</v>
+        <v>2.510293621329733</v>
       </c>
       <c r="E7">
         <v>23.50592341865877</v>
@@ -554,7 +554,7 @@
         <v>23.13346909257004</v>
       </c>
       <c r="D8">
-        <v>1.556513367399837</v>
+        <v>2.432339223923434</v>
       </c>
       <c r="E8">
         <v>25.03114082605749</v>
@@ -579,7 +579,7 @@
         <v>29.73984016323755</v>
       </c>
       <c r="D9">
-        <v>2.00785250938887</v>
+        <v>4.983898305084746</v>
       </c>
       <c r="E9">
         <v>13.3938706015891</v>
@@ -604,7 +604,7 @@
         <v>26.50241929828662</v>
       </c>
       <c r="D10">
-        <v>1.58547974650706</v>
+        <v>2.734483860658357</v>
       </c>
       <c r="E10">
         <v>22.42560632991228</v>
@@ -629,7 +629,7 @@
         <v>30.51350833493006</v>
       </c>
       <c r="D11">
-        <v>1.60510533599877</v>
+        <v>3.1458710066305</v>
       </c>
       <c r="E11">
         <v>19.58562068354879</v>
@@ -654,7 +654,7 @@
         <v>29.78483862897173</v>
       </c>
       <c r="D12">
-        <v>1.609746274667741</v>
+        <v>3.092456479690522</v>
       </c>
       <c r="E12">
         <v>19.94598765432099</v>
@@ -679,7 +679,7 @@
         <v>27.29000380083618</v>
       </c>
       <c r="D13">
-        <v>1.596093181266683</v>
+        <v>2.827815993121238</v>
       </c>
       <c r="E13">
         <v>21.74136561200168</v>
@@ -704,7 +704,7 @@
         <v>26.83846886912325</v>
       </c>
       <c r="D14">
-        <v>1.491413004856094</v>
+        <v>2.486817418781475</v>
       </c>
       <c r="E14">
         <v>24.07178512003803</v>
@@ -729,7 +729,7 @@
         <v>25.2327221438646</v>
       </c>
       <c r="D15">
-        <v>1.618721461187214</v>
+        <v>2.73639521420301</v>
       </c>
       <c r="E15">
         <v>22.58936355710549</v>
@@ -754,7 +754,7 @@
         <v>26.51978784169727</v>
       </c>
       <c r="D16">
-        <v>1.442188879082083</v>
+        <v>2.335397808480228</v>
       </c>
       <c r="E16">
         <v>25.286110107216</v>
@@ -779,7 +779,7 @@
         <v>28.83947185545518</v>
       </c>
       <c r="D17">
-        <v>1.336429068957511</v>
+        <v>2.174537211938043</v>
       </c>
       <c r="E17">
         <v>26.30428301699294</v>
@@ -804,7 +804,7 @@
         <v>25.82103043085267</v>
       </c>
       <c r="D18">
-        <v>1.415050095928374</v>
+        <v>2.229761504870675</v>
       </c>
       <c r="E18">
         <v>26.27769441256951</v>
@@ -829,7 +829,7 @@
         <v>25.45252637423653</v>
       </c>
       <c r="D19">
-        <v>1.598169464023123</v>
+        <v>2.694033678092145</v>
       </c>
       <c r="E19">
         <v>22.83244045005221</v>
@@ -854,7 +854,7 @@
         <v>26.82529335071708</v>
       </c>
       <c r="D20">
-        <v>1.730400451212634</v>
+        <v>3.229473684210526</v>
       </c>
       <c r="E20">
         <v>19.62404461888039</v>
@@ -879,7 +879,7 @@
         <v>27.02898550724638</v>
       </c>
       <c r="D21">
-        <v>1.607829430269136</v>
+        <v>2.843601895734597</v>
       </c>
       <c r="E21">
         <v>21.68163338247777</v>
@@ -904,7 +904,7 @@
         <v>29.25157907281611</v>
       </c>
       <c r="D22">
-        <v>1.644810349897089</v>
+        <v>3.17000377786173</v>
       </c>
       <c r="E22">
         <v>19.6183064665555</v>
@@ -929,7 +929,7 @@
         <v>27.45936098654709</v>
       </c>
       <c r="D23">
-        <v>1.455880852800163</v>
+        <v>2.42556084296397</v>
       </c>
       <c r="E23">
         <v>24.44029075804777</v>
@@ -954,7 +954,7 @@
         <v>27.12390361293183</v>
       </c>
       <c r="D24">
-        <v>1.577827183932452</v>
+        <v>2.75828638805188</v>
       </c>
       <c r="E24">
         <v>22.19045865514133</v>
@@ -979,7 +979,7 @@
         <v>25.62801530527367</v>
       </c>
       <c r="D25">
-        <v>1.233531705315001</v>
+        <v>1.803750937734434</v>
       </c>
       <c r="E25">
         <v>30.61833884601249</v>
@@ -1004,7 +1004,7 @@
         <v>29.60460460460461</v>
       </c>
       <c r="D26">
-        <v>1.325702911171933</v>
+        <v>2.182116040955631</v>
       </c>
       <c r="E26">
         <v>26.12246353553724</v>
@@ -1029,7 +1029,7 @@
         <v>27.25014025807486</v>
       </c>
       <c r="D27">
-        <v>1.202254769705146</v>
+        <v>1.78804815133276</v>
       </c>
       <c r="E27">
         <v>30.53161233865675</v>
@@ -1054,7 +1054,7 @@
         <v>26.20624408703879</v>
       </c>
       <c r="D28">
-        <v>1.155650531756287</v>
+        <v>1.657684630738523</v>
       </c>
       <c r="E28">
         <v>32.34046477314644</v>
@@ -1079,7 +1079,7 @@
         <v>24.08474079859416</v>
       </c>
       <c r="D29">
-        <v>1.579247610237434</v>
+        <v>2.548643941278925</v>
       </c>
       <c r="E29">
         <v>24.02414968019606</v>
@@ -1104,7 +1104,7 @@
         <v>28.17357640877758</v>
       </c>
       <c r="D30">
-        <v>1.613159152461367</v>
+        <v>2.957128672390632</v>
       </c>
       <c r="E30">
         <v>20.87570414807228</v>
@@ -1129,7 +1129,7 @@
         <v>28.00629590766002</v>
       </c>
       <c r="D31">
-        <v>1.542071197411003</v>
+        <v>2.714326402734264</v>
       </c>
       <c r="E31">
         <v>22.34882240611076</v>
@@ -1154,7 +1154,7 @@
         <v>31.3625304136253</v>
       </c>
       <c r="D32">
-        <v>1.924607820182627</v>
+        <v>4.855286473715299</v>
       </c>
       <c r="E32">
         <v>13.55375870626851</v>
@@ -1179,7 +1179,7 @@
         <v>19.76907913263869</v>
       </c>
       <c r="D33">
-        <v>2.079648609077599</v>
+        <v>3.531576330183988</v>
       </c>
       <c r="E33">
         <v>19.12142245887611</v>
@@ -1204,7 +1204,7 @@
         <v>27.47691761363636</v>
       </c>
       <c r="D34">
-        <v>1.441884280593958</v>
+        <v>2.387958448166208</v>
       </c>
       <c r="E34">
         <v>24.72740616481443</v>
@@ -1229,7 +1229,7 @@
         <v>27.47833017834014</v>
       </c>
       <c r="D35">
-        <v>1.538945108862312</v>
+        <v>2.666578108395324</v>
       </c>
       <c r="E35">
         <v>22.73084123437405</v>
@@ -1254,7 +1254,7 @@
         <v>23.40596396849662</v>
       </c>
       <c r="D36">
-        <v>1.553704845086514</v>
+        <v>2.441625324828727</v>
       </c>
       <c r="E36">
         <v>24.91832229580574</v>
@@ -1279,7 +1279,7 @@
         <v>26.95956208981744</v>
       </c>
       <c r="D37">
-        <v>1.55501582066937</v>
+        <v>2.677486187845304</v>
       </c>
       <c r="E37">
         <v>22.73076118049257</v>
@@ -1304,7 +1304,7 @@
         <v>27.33784321528054</v>
       </c>
       <c r="D38">
-        <v>1.372623989512781</v>
+        <v>2.197062423500612</v>
       </c>
       <c r="E38">
         <v>26.33178323127215</v>
@@ -1329,7 +1329,7 @@
         <v>27.00667199789934</v>
       </c>
       <c r="D39">
-        <v>1.546582245768187</v>
+        <v>2.655899321625563</v>
       </c>
       <c r="E39">
         <v>22.86671112528632</v>

--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_valparaiso.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>24.01511121142261</v>
+      </c>
+      <c r="C2">
         <v>39.12739740014079</v>
-      </c>
-      <c r="C2">
-        <v>24.01511121142261</v>
       </c>
       <c r="D2">
         <v>2.555753938278557</v>
       </c>
       <c r="E2">
-        <v>23.9835697839499</v>
+        <v>14.72032728674153</v>
       </c>
       <c r="F2">
         <v>61.29610292930857</v>
       </c>
       <c r="G2">
-        <v>14.72032728674153</v>
+        <v>23.9835697839499</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>25.66312681556265</v>
+      </c>
+      <c r="C3">
         <v>34.60640982903948</v>
-      </c>
-      <c r="C3">
-        <v>25.66312681556265</v>
       </c>
       <c r="D3">
         <v>2.889638089995872</v>
       </c>
       <c r="E3">
-        <v>21.59263110979052</v>
+        <v>16.01247957212896</v>
       </c>
       <c r="F3">
         <v>62.39488931808053</v>
       </c>
       <c r="G3">
-        <v>16.01247957212896</v>
+        <v>21.59263110979052</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>23.3457249070632</v>
+      </c>
+      <c r="C4">
         <v>35.37889619674006</v>
-      </c>
-      <c r="C4">
-        <v>23.3457249070632</v>
       </c>
       <c r="D4">
         <v>2.826543808600065</v>
       </c>
       <c r="E4">
-        <v>22.28948221813858</v>
+        <v>14.70831982128058</v>
       </c>
       <c r="F4">
         <v>63.00219796058084</v>
       </c>
       <c r="G4">
-        <v>14.70831982128058</v>
+        <v>22.28948221813858</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>31.23844731977819</v>
+      </c>
+      <c r="C5">
         <v>34.75046210720888</v>
-      </c>
-      <c r="C5">
-        <v>31.23844731977819</v>
       </c>
       <c r="D5">
         <v>2.877659574468085</v>
       </c>
       <c r="E5">
-        <v>20.93541202672606</v>
+        <v>18.8195991091314</v>
       </c>
       <c r="F5">
         <v>60.24498886414254</v>
       </c>
       <c r="G5">
-        <v>18.8195991091314</v>
+        <v>20.93541202672606</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>27.90387182910548</v>
+      </c>
+      <c r="C6">
         <v>42.39938966240702</v>
-      </c>
-      <c r="C6">
-        <v>27.90387182910548</v>
       </c>
       <c r="D6">
         <v>2.358524516419253</v>
       </c>
       <c r="E6">
-        <v>24.89640497256132</v>
+        <v>16.38481352895061</v>
       </c>
       <c r="F6">
         <v>58.71878149848807</v>
       </c>
       <c r="G6">
-        <v>16.38481352895061</v>
+        <v>24.89640497256132</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>29.63610289504347</v>
+      </c>
+      <c r="C7">
         <v>39.83597741328314</v>
-      </c>
-      <c r="C7">
-        <v>29.63610289504347</v>
       </c>
       <c r="D7">
         <v>2.510293621329733</v>
       </c>
       <c r="E7">
-        <v>23.50592341865877</v>
+        <v>17.48730696001693</v>
       </c>
       <c r="F7">
         <v>59.00676962132431</v>
       </c>
       <c r="G7">
-        <v>17.48730696001693</v>
+        <v>23.50592341865877</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>23.13346909257004</v>
+      </c>
+      <c r="C8">
         <v>41.11268651035323</v>
-      </c>
-      <c r="C8">
-        <v>23.13346909257004</v>
       </c>
       <c r="D8">
         <v>2.432339223923434</v>
       </c>
       <c r="E8">
-        <v>25.03114082605749</v>
+        <v>14.08463352317167</v>
       </c>
       <c r="F8">
         <v>60.88422565077084</v>
       </c>
       <c r="G8">
-        <v>14.08463352317167</v>
+        <v>25.03114082605749</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>29.73984016323755</v>
+      </c>
+      <c r="C9">
         <v>20.06461486141813</v>
-      </c>
-      <c r="C9">
-        <v>29.73984016323755</v>
       </c>
       <c r="D9">
         <v>4.983898305084746</v>
       </c>
       <c r="E9">
-        <v>13.3938706015891</v>
+        <v>19.85244040862656</v>
       </c>
       <c r="F9">
         <v>66.75368898978434</v>
       </c>
       <c r="G9">
-        <v>19.85244040862656</v>
+        <v>13.3938706015891</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>26.50241929828662</v>
+      </c>
+      <c r="C10">
         <v>36.56997265141067</v>
-      </c>
-      <c r="C10">
-        <v>26.50241929828662</v>
       </c>
       <c r="D10">
         <v>2.734483860658357</v>
       </c>
       <c r="E10">
-        <v>22.42560632991228</v>
+        <v>16.25193509546471</v>
       </c>
       <c r="F10">
-        <v>61.32245857462302</v>
+        <v>61.32245857462301</v>
       </c>
       <c r="G10">
-        <v>16.25193509546471</v>
+        <v>22.42560632991227</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>30.51350833493006</v>
+      </c>
+      <c r="C11">
         <v>31.7876987928722</v>
-      </c>
-      <c r="C11">
-        <v>30.51350833493006</v>
       </c>
       <c r="D11">
         <v>3.1458710066305</v>
       </c>
       <c r="E11">
-        <v>19.58562068354879</v>
+        <v>18.80054306121244</v>
       </c>
       <c r="F11">
         <v>61.61383625523877</v>
       </c>
       <c r="G11">
-        <v>18.80054306121244</v>
+        <v>19.58562068354879</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>29.78483862897173</v>
+      </c>
+      <c r="C12">
         <v>32.33675256442331</v>
-      </c>
-      <c r="C12">
-        <v>29.78483862897173</v>
       </c>
       <c r="D12">
         <v>3.092456479690522</v>
       </c>
       <c r="E12">
-        <v>19.94598765432099</v>
+        <v>18.37191358024691</v>
       </c>
       <c r="F12">
         <v>61.6820987654321</v>
       </c>
       <c r="G12">
-        <v>18.37191358024691</v>
+        <v>19.94598765432099</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>27.29000380083618</v>
+      </c>
+      <c r="C13">
         <v>35.36297985556823</v>
-      </c>
-      <c r="C13">
-        <v>27.29000380083618</v>
       </c>
       <c r="D13">
         <v>2.827815993121238</v>
       </c>
       <c r="E13">
-        <v>21.74136561200168</v>
+        <v>16.77805299808384</v>
       </c>
       <c r="F13">
         <v>61.48058138991447</v>
       </c>
       <c r="G13">
-        <v>16.77805299808384</v>
+        <v>21.74136561200168</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>26.83846886912325</v>
+      </c>
+      <c r="C14">
         <v>40.21203939008895</v>
-      </c>
-      <c r="C14">
-        <v>26.83846886912325</v>
       </c>
       <c r="D14">
         <v>2.486817418781475</v>
       </c>
       <c r="E14">
-        <v>24.07178512003803</v>
+        <v>16.06608034228666</v>
       </c>
       <c r="F14">
         <v>59.8621345376753</v>
       </c>
       <c r="G14">
-        <v>16.06608034228666</v>
+        <v>24.07178512003803</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>25.2327221438646</v>
+      </c>
+      <c r="C15">
         <v>36.54442877291961</v>
-      </c>
-      <c r="C15">
-        <v>25.2327221438646</v>
       </c>
       <c r="D15">
         <v>2.73639521420301</v>
       </c>
       <c r="E15">
-        <v>22.58936355710549</v>
+        <v>15.59721011333914</v>
       </c>
       <c r="F15">
         <v>61.81342632955536</v>
       </c>
       <c r="G15">
-        <v>15.59721011333914</v>
+        <v>22.58936355710549</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>26.51978784169727</v>
+      </c>
+      <c r="C16">
         <v>42.81925744594044</v>
-      </c>
-      <c r="C16">
-        <v>26.51978784169727</v>
       </c>
       <c r="D16">
         <v>2.335397808480228</v>
       </c>
       <c r="E16">
-        <v>25.286110107216</v>
+        <v>15.660763763402</v>
       </c>
       <c r="F16">
         <v>59.053126129382</v>
       </c>
       <c r="G16">
-        <v>15.660763763402</v>
+        <v>25.286110107216</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>28.83947185545518</v>
+      </c>
+      <c r="C17">
         <v>45.98679638637943</v>
-      </c>
-      <c r="C17">
-        <v>28.83947185545518</v>
       </c>
       <c r="D17">
         <v>2.174537211938043</v>
       </c>
       <c r="E17">
-        <v>26.30428301699294</v>
+        <v>16.496074729206</v>
       </c>
       <c r="F17">
         <v>57.19964225380105</v>
       </c>
       <c r="G17">
-        <v>16.496074729206</v>
+        <v>26.30428301699294</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>25.82103043085267</v>
+      </c>
+      <c r="C18">
         <v>44.84784573666767</v>
-      </c>
-      <c r="C18">
-        <v>25.82103043085267</v>
       </c>
       <c r="D18">
         <v>2.229761504870675</v>
       </c>
       <c r="E18">
-        <v>26.27769441256951</v>
+        <v>15.12931414952776</v>
       </c>
       <c r="F18">
         <v>58.59299143790273</v>
       </c>
       <c r="G18">
-        <v>15.12931414952776</v>
+        <v>26.27769441256951</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>25.45252637423653</v>
+      </c>
+      <c r="C19">
         <v>37.1190608392163</v>
-      </c>
-      <c r="C19">
-        <v>25.45252637423653</v>
       </c>
       <c r="D19">
         <v>2.694033678092145</v>
       </c>
       <c r="E19">
-        <v>22.83244045005221</v>
+        <v>15.65619602447379</v>
       </c>
       <c r="F19">
         <v>61.51136352547402</v>
       </c>
       <c r="G19">
-        <v>15.65619602447379</v>
+        <v>22.83244045005221</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>26.82529335071708</v>
+      </c>
+      <c r="C20">
         <v>30.96479791395045</v>
-      </c>
-      <c r="C20">
-        <v>26.82529335071708</v>
       </c>
       <c r="D20">
         <v>3.229473684210526</v>
       </c>
       <c r="E20">
+        <v>17.00061970667218</v>
+      </c>
+      <c r="F20">
+        <v>63.37533567444743</v>
+      </c>
+      <c r="G20">
         <v>19.62404461888039</v>
-      </c>
-      <c r="F20">
-        <v>63.37533567444742</v>
-      </c>
-      <c r="G20">
-        <v>17.00061970667217</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>27.02898550724638</v>
+      </c>
+      <c r="C21">
         <v>35.16666666666667</v>
-      </c>
-      <c r="C21">
-        <v>27.02898550724638</v>
       </c>
       <c r="D21">
         <v>2.843601895734597</v>
       </c>
       <c r="E21">
-        <v>21.68163338247777</v>
+        <v>16.6644328284859</v>
       </c>
       <c r="F21">
         <v>61.65393378903632</v>
       </c>
       <c r="G21">
-        <v>16.6644328284859</v>
+        <v>21.68163338247777</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>29.25157907281611</v>
+      </c>
+      <c r="C22">
         <v>31.54570373018711</v>
-      </c>
-      <c r="C22">
-        <v>29.25157907281611</v>
       </c>
       <c r="D22">
         <v>3.17000377786173</v>
       </c>
       <c r="E22">
-        <v>19.6183064665555</v>
+        <v>18.19158791921437</v>
       </c>
       <c r="F22">
-        <v>62.19010561423013</v>
+        <v>62.19010561423012</v>
       </c>
       <c r="G22">
-        <v>18.19158791921438</v>
+        <v>19.61830646655549</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>27.45936098654709</v>
+      </c>
+      <c r="C23">
         <v>41.22757847533632</v>
-      </c>
-      <c r="C23">
-        <v>27.45936098654709</v>
       </c>
       <c r="D23">
         <v>2.42556084296397</v>
       </c>
       <c r="E23">
-        <v>24.44029075804777</v>
+        <v>16.27829698857736</v>
       </c>
       <c r="F23">
         <v>59.28141225337487</v>
       </c>
       <c r="G23">
-        <v>16.27829698857736</v>
+        <v>24.44029075804777</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>27.12390361293183</v>
+      </c>
+      <c r="C24">
         <v>36.25439346442481</v>
-      </c>
-      <c r="C24">
-        <v>27.12390361293183</v>
       </c>
       <c r="D24">
         <v>2.75828638805188</v>
       </c>
       <c r="E24">
-        <v>22.19045865514133</v>
+        <v>16.60190129175428</v>
       </c>
       <c r="F24">
         <v>61.20764005310437</v>
       </c>
       <c r="G24">
-        <v>16.60190129175428</v>
+        <v>22.19045865514133</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>25.62801530527367</v>
+      </c>
+      <c r="C25">
         <v>55.44002661786725</v>
-      </c>
-      <c r="C25">
-        <v>25.62801530527367</v>
       </c>
       <c r="D25">
         <v>1.803750937734434</v>
       </c>
       <c r="E25">
-        <v>30.61833884601249</v>
+        <v>14.15380374862183</v>
       </c>
       <c r="F25">
         <v>55.22785740536567</v>
       </c>
       <c r="G25">
-        <v>14.15380374862183</v>
+        <v>30.61833884601249</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>29.60460460460461</v>
+      </c>
+      <c r="C26">
         <v>45.82707707707708</v>
-      </c>
-      <c r="C26">
-        <v>29.60460460460461</v>
       </c>
       <c r="D26">
         <v>2.182116040955631</v>
       </c>
       <c r="E26">
-        <v>26.12246353553724</v>
+        <v>16.87528975428836</v>
       </c>
       <c r="F26">
         <v>57.00224671017438</v>
       </c>
       <c r="G26">
-        <v>16.87528975428836</v>
+        <v>26.12246353553724</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>27.25014025807486</v>
+      </c>
+      <c r="C27">
         <v>55.92690550613128</v>
-      </c>
-      <c r="C27">
-        <v>27.25014025807486</v>
       </c>
       <c r="D27">
         <v>1.78804815133276</v>
       </c>
       <c r="E27">
-        <v>30.53161233865675</v>
+        <v>14.87639466199956</v>
       </c>
       <c r="F27">
         <v>54.5919929993437</v>
       </c>
       <c r="G27">
-        <v>14.87639466199956</v>
+        <v>30.53161233865675</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>26.20624408703879</v>
+      </c>
+      <c r="C28">
         <v>60.32510535821795</v>
-      </c>
-      <c r="C28">
-        <v>26.20624408703879</v>
       </c>
       <c r="D28">
         <v>1.657684630738523</v>
       </c>
       <c r="E28">
-        <v>32.34046477314644</v>
+        <v>14.04924382146809</v>
       </c>
       <c r="F28">
         <v>53.61029140538547</v>
       </c>
       <c r="G28">
-        <v>14.04924382146809</v>
+        <v>32.34046477314644</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>24.08474079859416</v>
+      </c>
+      <c r="C29">
         <v>39.23655179146734</v>
-      </c>
-      <c r="C29">
-        <v>24.08474079859416</v>
       </c>
       <c r="D29">
         <v>2.548643941278925</v>
       </c>
       <c r="E29">
-        <v>24.02414968019606</v>
+        <v>14.7468467929942</v>
       </c>
       <c r="F29">
         <v>61.22900352680973</v>
       </c>
       <c r="G29">
-        <v>14.7468467929942</v>
+        <v>24.02414968019606</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>28.17357640877758</v>
+      </c>
+      <c r="C30">
         <v>33.81658733137135</v>
-      </c>
-      <c r="C30">
-        <v>28.17357640877758</v>
       </c>
       <c r="D30">
         <v>2.957128672390632</v>
       </c>
       <c r="E30">
-        <v>20.87570414807228</v>
+        <v>17.39215255931914</v>
       </c>
       <c r="F30">
         <v>61.73214329260857</v>
       </c>
       <c r="G30">
-        <v>17.39215255931914</v>
+        <v>20.87570414807228</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>28.00629590766002</v>
+      </c>
+      <c r="C31">
         <v>36.84155299055614</v>
-      </c>
-      <c r="C31">
-        <v>28.00629590766002</v>
       </c>
       <c r="D31">
         <v>2.714326402734264</v>
       </c>
       <c r="E31">
+        <v>16.98917886696372</v>
+      </c>
+      <c r="F31">
+        <v>60.66199872692552</v>
+      </c>
+      <c r="G31">
         <v>22.34882240611076</v>
-      </c>
-      <c r="F31">
-        <v>60.66199872692553</v>
-      </c>
-      <c r="G31">
-        <v>16.98917886696372</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>31.3625304136253</v>
+      </c>
+      <c r="C32">
         <v>20.59610705596107</v>
-      </c>
-      <c r="C32">
-        <v>31.3625304136253</v>
       </c>
       <c r="D32">
         <v>4.855286473715299</v>
       </c>
       <c r="E32">
+        <v>20.63885997918501</v>
+      </c>
+      <c r="F32">
+        <v>65.80738131454646</v>
+      </c>
+      <c r="G32">
         <v>13.55375870626851</v>
-      </c>
-      <c r="F32">
-        <v>65.80738131454648</v>
-      </c>
-      <c r="G32">
-        <v>20.63885997918501</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>19.76907913263869</v>
+      </c>
+      <c r="C33">
         <v>28.31596733314559</v>
-      </c>
-      <c r="C33">
-        <v>19.76907913263869</v>
       </c>
       <c r="D33">
         <v>3.531576330183988</v>
       </c>
       <c r="E33">
-        <v>19.12142245887611</v>
+        <v>13.34981458590853</v>
       </c>
       <c r="F33">
         <v>67.52876295521537</v>
       </c>
       <c r="G33">
-        <v>13.34981458590853</v>
+        <v>19.12142245887611</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>27.47691761363636</v>
+      </c>
+      <c r="C34">
         <v>41.87677556818182</v>
-      </c>
-      <c r="C34">
-        <v>27.47691761363636</v>
       </c>
       <c r="D34">
         <v>2.387958448166208</v>
       </c>
       <c r="E34">
-        <v>24.72740616481443</v>
+        <v>16.22457538267981</v>
       </c>
       <c r="F34">
         <v>59.04801845250577</v>
       </c>
       <c r="G34">
-        <v>16.22457538267981</v>
+        <v>24.72740616481443</v>
       </c>
     </row>
     <row r="35">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="B35">
+        <v>27.47833017834014</v>
+      </c>
+      <c r="C35">
         <v>37.50124539204941</v>
-      </c>
-      <c r="C35">
-        <v>27.47833017834014</v>
       </c>
       <c r="D35">
         <v>2.666578108395324</v>
       </c>
       <c r="E35">
-        <v>22.73084123437405</v>
+        <v>16.65559514463434</v>
       </c>
       <c r="F35">
         <v>60.61356362099161</v>
       </c>
       <c r="G35">
-        <v>16.65559514463434</v>
+        <v>22.73084123437405</v>
       </c>
     </row>
     <row r="36">
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="B36">
+        <v>23.40596396849662</v>
+      </c>
+      <c r="C36">
         <v>40.95632486405945</v>
-      </c>
-      <c r="C36">
-        <v>23.40596396849662</v>
       </c>
       <c r="D36">
         <v>2.441625324828727</v>
       </c>
       <c r="E36">
-        <v>24.91832229580574</v>
+        <v>14.24047093451067</v>
       </c>
       <c r="F36">
         <v>60.84120676968359</v>
       </c>
       <c r="G36">
-        <v>14.24047093451067</v>
+        <v>24.91832229580574</v>
       </c>
     </row>
     <row r="37">
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B37">
+        <v>26.95956208981744</v>
+      </c>
+      <c r="C37">
         <v>37.34846530822801</v>
-      </c>
-      <c r="C37">
-        <v>26.95956208981744</v>
       </c>
       <c r="D37">
         <v>2.677486187845304</v>
       </c>
       <c r="E37">
-        <v>22.73076118049257</v>
+        <v>16.40793971952836</v>
       </c>
       <c r="F37">
         <v>60.86129909997907</v>
       </c>
       <c r="G37">
-        <v>16.40793971952836</v>
+        <v>22.73076118049257</v>
       </c>
     </row>
     <row r="38">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="B38">
+        <v>27.33784321528054</v>
+      </c>
+      <c r="C38">
         <v>45.51532033426184</v>
-      </c>
-      <c r="C38">
-        <v>27.33784321528054</v>
       </c>
       <c r="D38">
         <v>2.197062423500612</v>
       </c>
       <c r="E38">
-        <v>26.33178323127215</v>
+        <v>15.81564528753626</v>
       </c>
       <c r="F38">
         <v>57.85257148119158</v>
       </c>
       <c r="G38">
-        <v>15.81564528753626</v>
+        <v>26.33178323127215</v>
       </c>
     </row>
     <row r="39">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B39">
+        <v>27.00667199789934</v>
+      </c>
+      <c r="C39">
         <v>37.65202964801929</v>
-      </c>
-      <c r="C39">
-        <v>27.00667199789934</v>
       </c>
       <c r="D39">
         <v>2.655899321625563</v>
       </c>
       <c r="E39">
-        <v>22.86671112528632</v>
+        <v>16.40160630925802</v>
       </c>
       <c r="F39">
         <v>60.73168256545565</v>
       </c>
       <c r="G39">
-        <v>16.40160630925802</v>
+        <v>22.86671112528632</v>
       </c>
     </row>
   </sheetData>
